--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.931849130755</v>
+        <v>6.813925483747687</v>
       </c>
       <c r="D2" t="n">
-        <v>42.33405014143012</v>
+        <v>6.879283147982394</v>
       </c>
       <c r="E2" t="n">
-        <v>14.30795861672711</v>
+        <v>2.325043275218155</v>
       </c>
       <c r="F2" t="n">
-        <v>9.254879987056697</v>
+        <v>1.503917997896713</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.06045573188834</v>
+        <v>6.022324056431855</v>
       </c>
       <c r="D3" t="n">
-        <v>37.31704879226351</v>
+        <v>6.064020428742821</v>
       </c>
       <c r="E3" t="n">
-        <v>14.30795861672711</v>
+        <v>2.325043275218155</v>
       </c>
       <c r="F3" t="n">
-        <v>9.254879987056697</v>
+        <v>1.503917997896713</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.201562118716424</v>
+        <v>0.520253844291419</v>
       </c>
       <c r="D4" t="n">
-        <v>34.84059573986624</v>
+        <v>5.661596807728264</v>
       </c>
       <c r="E4" t="n">
-        <v>14.30795861672711</v>
+        <v>2.325043275218155</v>
       </c>
       <c r="F4" t="n">
-        <v>9.254879987056697</v>
+        <v>1.503917997896713</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.37267012981722</v>
+        <v>8.023058896095298</v>
       </c>
       <c r="D5" t="n">
-        <v>49.48457265111603</v>
+        <v>8.041243055806355</v>
       </c>
       <c r="E5" t="n">
-        <v>14.30795861672711</v>
+        <v>2.325043275218155</v>
       </c>
       <c r="F5" t="n">
-        <v>9.254879987056697</v>
+        <v>1.503917997896713</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.00432239472135</v>
+        <v>2.92570238914222</v>
       </c>
       <c r="D6" t="n">
-        <v>17.86374627300919</v>
+        <v>2.902858769363994</v>
       </c>
       <c r="E6" t="n">
-        <v>14.30795861672711</v>
+        <v>2.325043275218155</v>
       </c>
       <c r="F6" t="n">
-        <v>9.254879987056697</v>
+        <v>1.503917997896713</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.24099870362662</v>
+        <v>5.076662289339326</v>
       </c>
       <c r="D7" t="n">
-        <v>34.69096929476469</v>
+        <v>5.637282510399262</v>
       </c>
       <c r="E7" t="n">
-        <v>14.30795861672711</v>
+        <v>2.325043275218155</v>
       </c>
       <c r="F7" t="n">
-        <v>9.254879987056697</v>
+        <v>1.503917997896713</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.59956858720312</v>
+        <v>4.647429895420507</v>
       </c>
       <c r="D8" t="n">
-        <v>28.92811542879403</v>
+        <v>4.70081875717903</v>
       </c>
       <c r="E8" t="n">
-        <v>14.30795861672711</v>
+        <v>2.325043275218155</v>
       </c>
       <c r="F8" t="n">
-        <v>9.254879987056697</v>
+        <v>1.503917997896713</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
